--- a/Week-01/Ex4A_GTrends.xlsx
+++ b/Week-01/Ex4A_GTrends.xlsx
@@ -1981,5 +1981,6 @@
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{E14D693E-090D-4D9D-BC12-6DC4E4556F2C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>